--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486465_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486465_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1721</v>
+        <v>4.2818</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1826</v>
+        <v>4.9532</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0104</v>
+        <v>-0.6714</v>
       </c>
       <c r="G2" t="n">
         <v>4.4059</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.8217</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5899</v>
+        <v>0.3605</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.5212</v>
+        <v>-1.1822</v>
       </c>
       <c r="V2" t="n">
         <v>-1.695</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. BOMBINO PARADA</t>
+          <t>L. CAPALBO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6622</v>
+        <v>3.5676</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0498</v>
+        <v>3.4727</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.3876</v>
+        <v>0.0949</v>
       </c>
       <c r="G3" t="n">
-        <v>4.169</v>
+        <v>5.512</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9929</v>
+        <v>0.079</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1761</v>
+        <v>5.433</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4131</v>
+        <v>6.7284</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4951</v>
+        <v>0.4507</v>
       </c>
       <c r="L3" t="n">
-        <v>0.918</v>
+        <v>6.2777</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2441</v>
+        <v>-1.2163</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5022</v>
+        <v>-0.3716</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2582</v>
+        <v>-0.8447</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2023</v>
+        <v>-1.9221</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1214</v>
+        <v>-0.9061</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0809</v>
+        <v>-1.0161</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8456</v>
+        <v>-0.1745</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.5851</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. CAPALBO</t>
+          <t>P. BOMBINO PARADA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5319</v>
+        <v>2.7046</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6219</v>
+        <v>5.9381</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.09</v>
+        <v>-3.2335</v>
       </c>
       <c r="G4" t="n">
-        <v>5.512</v>
+        <v>4.169</v>
       </c>
       <c r="H4" t="n">
-        <v>0.079</v>
+        <v>2.9929</v>
       </c>
       <c r="I4" t="n">
-        <v>5.433</v>
+        <v>1.1761</v>
       </c>
       <c r="J4" t="n">
-        <v>6.7284</v>
+        <v>4.4131</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4507</v>
+        <v>3.4951</v>
       </c>
       <c r="L4" t="n">
-        <v>6.2777</v>
+        <v>0.918</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2163</v>
+        <v>-0.2441</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3716</v>
+        <v>-0.5022</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8447</v>
+        <v>0.2582</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.9579</v>
+        <v>-1.1599</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7569</v>
+        <v>-0.2331</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.201</v>
+        <v>-0.9268</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1745</v>
+        <v>2.8456</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3698</v>
+        <v>-3.5851</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.861</v>
+        <v>0.7804</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8484</v>
+        <v>0.4654</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9874000000000001</v>
+        <v>0.315</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2107</v>
+        <v>0.8676</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1763</v>
+        <v>1.1864</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0343</v>
+        <v>-0.3187</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2025</v>
+        <v>0.9977</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3555</v>
+        <v>1.1076</v>
       </c>
       <c r="L5" t="n">
-        <v>0.153</v>
+        <v>-0.1099</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0082</v>
+        <v>-0.1301</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1792</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1873</v>
+        <v>-0.2088</v>
       </c>
       <c r="P5" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2011</v>
+        <v>-0.1541</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7904</v>
+        <v>0.5552</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4107</v>
+        <v>-0.7093</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.4345</v>
+        <v>-0.5857</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.695</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2875</v>
+        <v>0.4292</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6345</v>
+        <v>-0.6777</v>
       </c>
       <c r="F6" t="n">
-        <v>0.922</v>
+        <v>1.1069</v>
       </c>
       <c r="G6" t="n">
         <v>0.2652</v>
@@ -922,13 +922,13 @@
         <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1952</v>
+        <v>-0.0535</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0364</v>
+        <v>-0.8514</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1057</v>
+        <v>0.0677</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7514</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.7073</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4004</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5122</v>
+        <v>0.6856</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7006</v>
+        <v>0.8124</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1884</v>
+        <v>-0.1268</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0847</v>
+        <v>-1.2285</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8757</v>
+        <v>0.1287</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.209</v>
+        <v>-1.3572</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8676</v>
+        <v>-1.2107</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1864</v>
+        <v>-0.1763</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3187</v>
+        <v>-1.0343</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9977</v>
+        <v>-0.2025</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1076</v>
+        <v>-0.3555</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1099</v>
+        <v>0.153</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1301</v>
+        <v>-1.0082</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.1792</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2088</v>
+        <v>-1.1873</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.0192</v>
+        <v>1.1116</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7859</v>
+        <v>1.0707</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2333</v>
+        <v>0.0408</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5857</v>
+        <v>-2.4345</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5857</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3615</v>
+        <v>-3.0858</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0882</v>
+        <v>-0.6411</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2734</v>
+        <v>-2.4446</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0365</v>
@@ -1156,13 +1156,13 @@
         <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4124</v>
+        <v>-0.3118</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1524</v>
+        <v>-0.7054</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5648</v>
+        <v>0.3935</v>
       </c>
       <c r="V9" t="n">
         <v>-2.2599</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2078</v>
+        <v>-3.9043</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.746</v>
+        <v>-2.5658</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4618</v>
+        <v>-1.3385</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8773</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6579</v>
+        <v>-1.3543</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.5612</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9164</v>
+        <v>-0.7931</v>
       </c>
       <c r="V10" t="n">
         <v>-0.7602</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0048</v>
+        <v>-4.5201</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1679</v>
+        <v>-2.6523</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8369</v>
+        <v>-1.8678</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7103</v>
@@ -1312,13 +1312,13 @@
         <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.512</v>
+        <v>-0.0273</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.1694</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1729</v>
+        <v>0.1421</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2498</v>
+        <v>-0.9074000000000009</v>
       </c>
       <c r="E12" t="n">
-        <v>7.439</v>
+        <v>7.781600000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.688800000000001</v>
+        <v>-8.6889</v>
       </c>
       <c r="G12" t="n">
         <v>5.984499999999999</v>
@@ -1366,13 +1366,13 @@
         <v>12.2459</v>
       </c>
       <c r="K12" t="n">
-        <v>7.5003</v>
+        <v>7.500299999999999</v>
       </c>
       <c r="L12" t="n">
         <v>4.7456</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.261299999999999</v>
+        <v>-6.2613</v>
       </c>
       <c r="N12" t="n">
         <v>-1.6152</v>
@@ -1384,19 +1384,19 @@
         <v>6.5251</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.6126</v>
+        <v>-7.612599999999999</v>
       </c>
       <c r="R12" t="n">
         <v>14.1378</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.350200000000001</v>
+        <v>-4.0075</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6791</v>
+        <v>1.0215</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.0292</v>
+        <v>-5.029299999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-9.409600000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7219</v>
+        <v>6.3332</v>
       </c>
       <c r="E13" t="n">
         <v>7.6287</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9069</v>
+        <v>-1.2955</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7331</v>
@@ -1468,13 +1468,13 @@
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6099</v>
+        <v>1.2212</v>
       </c>
       <c r="T13" t="n">
         <v>1.0827</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4729</v>
+        <v>0.1385</v>
       </c>
       <c r="V13" t="n">
         <v>5.8451</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>I. TAMBA VILLEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7549</v>
+        <v>2.3078</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3548</v>
+        <v>1.2362</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5999</v>
+        <v>1.0716</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.0861</v>
+        <v>1.9533</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.1808</v>
+        <v>1.7397</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.9053</v>
+        <v>0.2136</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.6952</v>
+        <v>1.4417</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.2521</v>
+        <v>1.4417</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.4431</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3909</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9287</v>
+        <v>0.298</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4622</v>
+        <v>0.2136</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7562</v>
+        <v>0.137</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8575</v>
+        <v>-0.2055</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.3425</v>
       </c>
       <c r="V14" t="n">
-        <v>5.0849</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>5.2801</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. TAMBA VILLEN</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3078</v>
+        <v>1.5905</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2362</v>
+        <v>2.2314</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0716</v>
+        <v>-0.6409</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9533</v>
+        <v>-6.0861</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7397</v>
+        <v>-3.1808</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2136</v>
+        <v>-2.9053</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4417</v>
+        <v>-3.6952</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4417</v>
+        <v>-1.2521</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-2.4431</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5116000000000001</v>
+        <v>-2.3909</v>
       </c>
       <c r="N15" t="n">
-        <v>0.298</v>
+        <v>-1.9287</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2136</v>
+        <v>-0.4622</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>0.137</v>
+        <v>2.5918</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2055</v>
+        <v>1.7341</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3425</v>
+        <v>0.8577</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.0849</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>5.2801</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7423999999999999</v>
+        <v>1.3565</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3554</v>
+        <v>0.232</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0978</v>
+        <v>1.1244</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8531</v>
+        <v>-0.907</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7727000000000001</v>
+        <v>1.0461</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0805</v>
+        <v>-1.9531</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8434</v>
+        <v>-0.0159</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6538</v>
+        <v>1.6639</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1896</v>
+        <v>-1.6797</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0097</v>
+        <v>-0.8911</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1188</v>
+        <v>-0.6178</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1091</v>
+        <v>-0.2733</v>
       </c>
       <c r="P16" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.144</v>
+        <v>1.5457</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0769</v>
+        <v>0.6177</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0.928</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3045</v>
+        <v>-0.3698</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.3698</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5577</v>
+        <v>1.2283</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0294</v>
+        <v>1.253</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4717</v>
+        <v>-0.0247</v>
       </c>
       <c r="G17" t="n">
         <v>1.1125</v>
@@ -1780,13 +1780,13 @@
         <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6201</v>
+        <v>0.0505</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0769</v>
+        <v>0.1466</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5432</v>
+        <v>-0.0961</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3698</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0178</v>
+        <v>0.6821</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3326</v>
+        <v>-0.4671</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3504</v>
+        <v>1.1492</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.907</v>
+        <v>-0.8531</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0461</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9531</v>
+        <v>-0.0805</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0159</v>
+        <v>-0.8434</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6639</v>
+        <v>-0.6538</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.6797</v>
+        <v>-0.1896</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8911</v>
+        <v>-0.0097</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6178</v>
+        <v>-0.1188</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2733</v>
+        <v>0.1091</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.207</v>
+        <v>-0.2043</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9469</v>
+        <v>-0.1887</v>
       </c>
       <c r="U18" t="n">
-        <v>1.154</v>
+        <v>-0.0156</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3698</v>
+        <v>1.3045</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3698</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1951</v>
+        <v>0.1209</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3648</v>
+        <v>-0.1413</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1698</v>
+        <v>0.2622</v>
       </c>
       <c r="G19" t="n">
         <v>1.4953</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6029</v>
+        <v>-0.2869</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4795</v>
+        <v>-0.256</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1234</v>
+        <v>-0.031</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3493</v>
+        <v>-0.3788</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0757</v>
+        <v>-0.0361</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.425</v>
+        <v>-0.3427</v>
       </c>
       <c r="G20" t="n">
         <v>1.7659</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1799</v>
+        <v>-0.2094</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1286</v>
+        <v>0.0168</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3085</v>
+        <v>-0.2262</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1952</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. GEU</t>
+          <t>Y. JOSEPH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7062</v>
+        <v>-1.9682</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4709</v>
+        <v>-3.1233</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1771</v>
+        <v>1.1551</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8319</v>
+        <v>-0.8515</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1951</v>
+        <v>-0.6021</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6367</v>
+        <v>-0.2494</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7456</v>
+        <v>-0.7103</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4467</v>
+        <v>-0.1182</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2989</v>
+        <v>-0.5921</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0863</v>
+        <v>-0.1412</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7484</v>
+        <v>-0.4838</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3379</v>
+        <v>0.3426</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0875</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4084</v>
+        <v>0.4059</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1088</v>
+        <v>-0.2379</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2996</v>
+        <v>0.6438</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y. JOSEPH</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8674</v>
+        <v>-1.9877</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5703</v>
+        <v>1.7075</v>
       </c>
       <c r="F22" t="n">
-        <v>0.703</v>
+        <v>-3.6951</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8515</v>
+        <v>1.2313</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6021</v>
+        <v>-0.5687</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2494</v>
+        <v>1.8001</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7103</v>
+        <v>3.9864</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1182</v>
+        <v>0.4475</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5921</v>
+        <v>3.5389</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1412</v>
+        <v>-2.755</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4838</v>
+        <v>-1.0162</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3426</v>
+        <v>-1.7388</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5225</v>
+        <v>-1.305</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4933</v>
+        <v>-0.0445</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.6357</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1917</v>
+        <v>-0.6802</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.8695</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>U. MENDICOTE RUBIO</t>
+          <t>D. GEU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2911</v>
+        <v>-2.2529</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4032</v>
+        <v>-1.3172</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8879</v>
+        <v>-0.9357</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2803</v>
+        <v>-2.8319</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7911</v>
+        <v>-1.1951</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4893</v>
+        <v>-1.6367</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2548</v>
+        <v>-1.7456</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2587</v>
+        <v>-0.4467</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9961</v>
+        <v>-1.2989</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5351</v>
+        <v>-1.0863</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0497</v>
+        <v>-0.7484</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4854</v>
+        <v>-0.3379</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.9576</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2277</v>
+        <v>1.8617</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4747</v>
+        <v>1.3207</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7024</v>
+        <v>0.5411</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1745</v>
+        <v>-0.1952</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.9554</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>U. MENDICOTE RUBIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4437</v>
+        <v>-2.8017</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.5149</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.363</v>
+        <v>-2.2867</v>
       </c>
       <c r="G24" t="n">
-        <v>1.2313</v>
+        <v>-1.2803</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5687</v>
+        <v>-0.7911</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8001</v>
+        <v>-0.4893</v>
       </c>
       <c r="J24" t="n">
-        <v>3.9864</v>
+        <v>1.2548</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4475</v>
+        <v>0.2587</v>
       </c>
       <c r="L24" t="n">
-        <v>3.5389</v>
+        <v>0.9961</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.755</v>
+        <v>-2.5351</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0162</v>
+        <v>-1.0497</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.7388</v>
+        <v>-1.4854</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.305</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R24" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.5005</v>
+        <v>0.2617</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1524</v>
+        <v>0.3629</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3481</v>
+        <v>-0.1013</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.8695</v>
+        <v>0.1745</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.13</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="25">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.249700000000001</v>
+        <v>4.23</v>
       </c>
       <c r="E25" t="n">
-        <v>8.688700000000001</v>
+        <v>8.688899999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.4389</v>
+        <v>-4.4588</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.984699999999999</v>
+        <v>-5.9847</v>
       </c>
       <c r="H25" t="n">
         <v>-5.8851</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.09960000000000035</v>
+        <v>-0.09959999999999986</v>
       </c>
       <c r="J25" t="n">
-        <v>6.261399999999999</v>
+        <v>6.2614</v>
       </c>
       <c r="K25" t="n">
-        <v>1.615400000000001</v>
+        <v>1.6154</v>
       </c>
       <c r="L25" t="n">
-        <v>4.6459</v>
+        <v>4.645900000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-12.2459</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.500400000000001</v>
+        <v>-7.500399999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-4.745699999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-6.5252</v>
+        <v>-6.525199999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-14.1379</v>
       </c>
       <c r="R25" t="n">
-        <v>7.6125</v>
+        <v>7.612499999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>4.350099999999999</v>
+        <v>7.3304</v>
       </c>
       <c r="T25" t="n">
-        <v>5.029199999999999</v>
+        <v>5.0291</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6791000000000001</v>
+        <v>2.3012</v>
       </c>
       <c r="V25" t="n">
         <v>9.409500000000001</v>
